--- a/media/exports/reports/2026-10/growth-trades.xlsx
+++ b/media/exports/reports/2026-10/growth-trades.xlsx
@@ -818,7 +818,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
     <row r="9" ht="75" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>October is still in progress and wages are paid fortnightly, so a part month can't be bridged: this is September, the latest closed month. September's jobs made $73,107 gross margin (36.1%). Technician time not charged to jobs took $3,430 and overheads $59,580, leaving $10,097 profit before tax (5.0% of revenue). To cover overheads, jobs need a 31.1% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
+          <t>October is still in progress and wages are paid fortnightly, so a part month can't be bridged: this is September, the latest closed month. September's jobs made $96,230 gross margin (42.7%). Technician time not charged to jobs took $28,417 and overheads $59,580, leaving $8,233 profit before tax (3.7% of revenue). To cover overheads, jobs need a 39.0% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
     <row r="12" ht="90" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Gross margin is not profit. Job gross margin = revenue less materials, subcontractors and technician time charged to the job at $68 an hour (wages and all on-costs). Not included: technician time not charged to any job (travel, training, waiting), and overheads (office wages, marketing, vehicles, rent, insurance, IT, depreciation, interest). Profit is what's left after those. Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Gross margin is not profit. Job gross margin = revenue less materials, subcontractors and technician time charged to the job at $68 an hour (wages and all on-costs). Not included: technician time not charged to any job (travel, training, waiting), and overheads (office wages, marketing, vehicles, rent, insurance, IT, depreciation, interest). Profit is what's left after those. Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>$76,875 against $128,898</t>
+          <t>$86,031 against $143,566</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>$651,464 against $583,077</t>
+          <t>$726,624 against $650,349</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>$250,758 before overheads</t>
+          <t>$325,918 before overheads</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
     <row r="21" ht="45" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Revenue is 11.7% up on the same period last year, year to date ($651,464 against $583,077). Maintenance contracts make the highest gross margin (59.5%); Installations the lowest (28.8%). The business needs 31.1% gross margin just to cover overheads.</t>
+          <t>Revenue is 11.7% up on the same period last year, year to date ($726,624 against $650,349). Maintenance contracts make the highest gross margin (63.9%); Installations the lowest (36.5%). The business needs 39.0% gross margin just to cover overheads.</t>
         </is>
       </c>
     </row>
@@ -963,10 +963,10 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
+    <row r="24" ht="45" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Installations: 28.8% gross margin, 6.2 points under the 35.0% target: about $24,765 on $400,900 of revenue this financial year to date. It's below the 31.1% needed to cover overheads, too. Maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($39,764 ahead on $162,000 this financial year to date).</t>
+          <t>Installations: 36.5% gross margin, 1.5 points over the 35.0% target ($6,565 ahead on $449,100 this financial year to date). Maintenance contracts: 63.9% gross margin, 28.9 points over the 35.0% target ($52,374 ahead on $181,400 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>$40,500 against $35,800</t>
+          <t>$45,350 against $40,100</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>$162,000 against $135,400</t>
+          <t>$181,400 against $151,700</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>$96,464 before overheads</t>
+          <t>$115,864 before overheads</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
     <row r="33" ht="45" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Maintenance contracts brought in $162,000 this financial year to date, 19.6% on the same period last year (faster than the business as a whole, 11.7%), at a 59.5% gross margin (above the 38.5% overall).</t>
+          <t>Maintenance contracts brought in $181,400 this financial year to date, 19.6% on the same period last year (faster than the business as a whole, 11.7%), at a 63.9% gross margin (above the 44.9% overall).</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($39,764 ahead on $162,000 this financial year to date).</t>
+          <t>Maintenance contracts: 63.9% gross margin, 28.9 points over the 35.0% target ($52,374 ahead on $181,400 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>$33,000 against $70,800</t>
+          <t>$37,000 against $79,300</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>$400,900 against $367,900</t>
+          <t>$449,100 against $412,100</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>$115,550 before overheads</t>
+          <t>$163,750 before overheads</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
     <row r="45" ht="45" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Installations brought in $400,900 this financial year to date, 9.0% on the same period last year (slower than the business as a whole, 11.7%), at a 28.8% gross margin (below the 38.5% overall).</t>
+          <t>Installations brought in $449,100 this financial year to date, 9.0% on the same period last year (slower than the business as a whole, 11.7%), at a 36.5% gross margin (below the 44.9% overall).</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Installations: 28.8% gross margin, 6.2 points under the 35.0% target: about $24,765 on $400,900 of revenue this financial year to date. It's below the 31.1% needed to cover overheads, too.</t>
+          <t>Installations: 36.5% gross margin, 1.5 points over the 35.0% target ($6,565 ahead on $449,100 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>$3,375 against $22,298</t>
+          <t>$3,681 against $24,166</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>$88,564 against $79,777</t>
+          <t>$96,124 against $86,549</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>$38,744 before overheads</t>
+          <t>$46,304 before overheads</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
     <row r="57" ht="45" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Call-outs and repairs brought in $88,564 this financial year to date, 11.0% on the same period last year (slower than the business as a whole, 11.7%), at a 43.7% gross margin (above the 38.5% overall).</t>
+          <t>Call-outs and repairs brought in $96,124 this financial year to date, 11.1% on the same period last year (slower than the business as a whole, 11.7%), at a 48.2% gross margin (above the 44.9% overall).</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>Call-outs and repairs: 43.7% gross margin, 8.7 points over the 35.0% target ($7,747 ahead on $88,564 this financial year to date).</t>
+          <t>Call-outs and repairs: 48.2% gross margin, 13.2 points over the 35.0% target ($12,661 ahead on $96,124 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1360,7 +1360,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>73107</v>
+        <v>96230</v>
       </c>
     </row>
     <row r="9">
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>54600</v>
+        <v>79587</v>
       </c>
     </row>
     <row r="10">
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>202337</v>
+        <v>225460</v>
       </c>
     </row>
     <row r="16">
@@ -1506,7 +1506,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Ties to the September 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave. October is still in progress, so this uses September.</t>
+          <t>Ties to the September 2026 P&amp;L (locked). Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold. October is still in progress, so this uses September.</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="B25" s="12" t="n">
-        <v>76875</v>
+        <v>86031</v>
       </c>
     </row>
     <row r="26">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>128898</v>
+        <v>143566</v>
       </c>
     </row>
     <row r="27">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>651464</v>
+        <v>726624</v>
       </c>
     </row>
     <row r="35">
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="B35" s="12" t="n">
-        <v>583077</v>
+        <v>650349</v>
       </c>
     </row>
     <row r="36">
@@ -1634,7 +1634,7 @@
         </is>
       </c>
       <c r="B37" s="12" t="n">
-        <v>250758</v>
+        <v>325918</v>
       </c>
     </row>
     <row r="38">
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="B45" s="12" t="n">
-        <v>651464</v>
+        <v>726624</v>
       </c>
     </row>
     <row r="46">
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="B46" s="12" t="n">
-        <v>583077</v>
+        <v>650349</v>
       </c>
     </row>
     <row r="47">
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="B48" s="12" t="n">
-        <v>250758</v>
+        <v>325918</v>
       </c>
     </row>
     <row r="49">
@@ -1769,7 +1769,7 @@
         </is>
       </c>
       <c r="B56" s="12" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
     </row>
     <row r="57">
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="B57" s="12" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
     </row>
     <row r="58">
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B65" s="12" t="n">
-        <v>162000</v>
+        <v>181400</v>
       </c>
     </row>
     <row r="66">
@@ -1841,7 +1841,7 @@
         </is>
       </c>
       <c r="B66" s="12" t="n">
-        <v>135400</v>
+        <v>151700</v>
       </c>
     </row>
     <row r="67">
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="B68" s="12" t="n">
-        <v>96464</v>
+        <v>115864</v>
       </c>
     </row>
     <row r="69">
@@ -1914,7 +1914,7 @@
         </is>
       </c>
       <c r="B76" s="12" t="n">
-        <v>162000</v>
+        <v>181400</v>
       </c>
     </row>
     <row r="77">
@@ -1924,7 +1924,7 @@
         </is>
       </c>
       <c r="B77" s="12" t="n">
-        <v>135400</v>
+        <v>151700</v>
       </c>
     </row>
     <row r="78">
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="B79" s="12" t="n">
-        <v>96464</v>
+        <v>115864</v>
       </c>
     </row>
     <row r="80">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B87" s="12" t="n">
-        <v>33000</v>
+        <v>37000</v>
       </c>
     </row>
     <row r="88">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B88" s="12" t="n">
-        <v>70800</v>
+        <v>79300</v>
       </c>
     </row>
     <row r="89">
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="B96" s="12" t="n">
-        <v>400900</v>
+        <v>449100</v>
       </c>
     </row>
     <row r="97">
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="B97" s="12" t="n">
-        <v>367900</v>
+        <v>412100</v>
       </c>
     </row>
     <row r="98">
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="B99" s="12" t="n">
-        <v>115550</v>
+        <v>163750</v>
       </c>
     </row>
     <row r="100">
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="B107" s="12" t="n">
-        <v>400900</v>
+        <v>449100</v>
       </c>
     </row>
     <row r="108">
@@ -2152,7 +2152,7 @@
         </is>
       </c>
       <c r="B108" s="12" t="n">
-        <v>367900</v>
+        <v>412100</v>
       </c>
     </row>
     <row r="109">
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="B110" s="12" t="n">
-        <v>115550</v>
+        <v>163750</v>
       </c>
     </row>
     <row r="111">
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="B118" s="12" t="n">
-        <v>3375</v>
+        <v>3681</v>
       </c>
     </row>
     <row r="119">
@@ -2235,7 +2235,7 @@
         </is>
       </c>
       <c r="B119" s="12" t="n">
-        <v>22298</v>
+        <v>24166</v>
       </c>
     </row>
     <row r="120">
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="B127" s="12" t="n">
-        <v>88564</v>
+        <v>96124</v>
       </c>
     </row>
     <row r="128">
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="B128" s="12" t="n">
-        <v>79777</v>
+        <v>86549</v>
       </c>
     </row>
     <row r="129">
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="B130" s="12" t="n">
-        <v>38744</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="131">
@@ -2370,7 +2370,7 @@
         </is>
       </c>
       <c r="B138" s="12" t="n">
-        <v>88564</v>
+        <v>96124</v>
       </c>
     </row>
     <row r="139">
@@ -2380,7 +2380,7 @@
         </is>
       </c>
       <c r="B139" s="12" t="n">
-        <v>79777</v>
+        <v>86549</v>
       </c>
     </row>
     <row r="140">
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="B141" s="12" t="n">
-        <v>38744</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="142">
@@ -2431,7 +2431,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2481,7 +2481,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="D6" s="12" t="n">
-        <v>179474</v>
+        <v>200124</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>113016</v>
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="D7" s="12" t="n">
-        <v>143156</v>
+        <v>159406</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>85316</v>
@@ -2602,7 +2602,7 @@
         </is>
       </c>
       <c r="D8" s="12" t="n">
-        <v>140909</v>
+        <v>156794</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>80742</v>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>160943</v>
+        <v>179190</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>102348</v>
@@ -2664,7 +2664,7 @@
         </is>
       </c>
       <c r="D10" s="12" t="n">
-        <v>135082</v>
+        <v>150465</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>85752</v>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>124705</v>
+        <v>138865</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>76808</v>
@@ -2726,7 +2726,7 @@
         </is>
       </c>
       <c r="D12" s="12" t="n">
-        <v>129816</v>
+        <v>144649</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>83700</v>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="D13" s="12" t="n">
-        <v>164113</v>
+        <v>183265</v>
       </c>
       <c r="E13" s="12" t="n">
         <v>97584</v>
@@ -2788,7 +2788,7 @@
         </is>
       </c>
       <c r="D14" s="12" t="n">
-        <v>186760</v>
+        <v>208588</v>
       </c>
       <c r="E14" s="12" t="n">
         <v>120326</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="D15" s="12" t="n">
-        <v>139164</v>
+        <v>155118</v>
       </c>
       <c r="E15" s="12" t="n">
         <v>78258</v>
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="D16" s="12" t="n">
-        <v>128255</v>
+        <v>143077</v>
       </c>
       <c r="E16" s="12" t="n">
         <v>80054</v>
@@ -2881,7 +2881,7 @@
         </is>
       </c>
       <c r="D17" s="12" t="n">
-        <v>128898</v>
+        <v>143566</v>
       </c>
       <c r="E17" s="12" t="n">
         <v>79452</v>
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="D18" s="12" t="n">
-        <v>174786</v>
+        <v>194966</v>
       </c>
       <c r="E18" s="12" t="n">
         <v>115942</v>
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="D19" s="12" t="n">
-        <v>135079</v>
+        <v>150283</v>
       </c>
       <c r="E19" s="12" t="n">
         <v>84626</v>
@@ -2974,7 +2974,7 @@
         </is>
       </c>
       <c r="D20" s="12" t="n">
-        <v>164780</v>
+        <v>183306</v>
       </c>
       <c r="E20" s="12" t="n">
         <v>106590</v>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="D21" s="12" t="n">
-        <v>196372</v>
+        <v>218908</v>
       </c>
       <c r="E21" s="12" t="n">
         <v>120662</v>
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="D22" s="12" t="n">
-        <v>191500</v>
+        <v>213578</v>
       </c>
       <c r="E22" s="12" t="n">
         <v>123342</v>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="D23" s="12" t="n">
-        <v>164987</v>
+        <v>183967</v>
       </c>
       <c r="E23" s="12" t="n">
         <v>96144</v>
@@ -3098,7 +3098,7 @@
         </is>
       </c>
       <c r="D24" s="12" t="n">
-        <v>161963</v>
+        <v>180342</v>
       </c>
       <c r="E24" s="12" t="n">
         <v>98858</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>173163</v>
+        <v>193032</v>
       </c>
       <c r="E25" s="12" t="n">
         <v>106500</v>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="D26" s="12" t="n">
-        <v>193245</v>
+        <v>215610</v>
       </c>
       <c r="E26" s="12" t="n">
         <v>122124</v>
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="D27" s="12" t="n">
-        <v>179007</v>
+        <v>199523</v>
       </c>
       <c r="E27" s="12" t="n">
         <v>105370</v>
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="D28" s="12" t="n">
-        <v>202337</v>
+        <v>225460</v>
       </c>
       <c r="E28" s="12" t="n">
         <v>129230</v>
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="D29" s="12" t="n">
-        <v>76875</v>
+        <v>86031</v>
       </c>
       <c r="E29" s="12" t="n">
         <v>43982</v>
@@ -3284,7 +3284,7 @@
         </is>
       </c>
       <c r="D30" s="12" t="n">
-        <v>24670</v>
+        <v>27650</v>
       </c>
       <c r="E30" s="12" t="n">
         <v>10420</v>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="D31" s="12" t="n">
-        <v>24670</v>
+        <v>27650</v>
       </c>
       <c r="E31" s="12" t="n">
         <v>10420</v>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="D32" s="12" t="n">
-        <v>24670</v>
+        <v>27650</v>
       </c>
       <c r="E32" s="12" t="n">
         <v>10420</v>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="D33" s="12" t="n">
-        <v>27930</v>
+        <v>31300</v>
       </c>
       <c r="E33" s="12" t="n">
         <v>11782</v>
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="D34" s="12" t="n">
-        <v>27930</v>
+        <v>31300</v>
       </c>
       <c r="E34" s="12" t="n">
         <v>11782</v>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="D35" s="12" t="n">
-        <v>27930</v>
+        <v>31300</v>
       </c>
       <c r="E35" s="12" t="n">
         <v>11782</v>
@@ -3470,7 +3470,7 @@
         </is>
       </c>
       <c r="D36" s="12" t="n">
-        <v>27930</v>
+        <v>31300</v>
       </c>
       <c r="E36" s="12" t="n">
         <v>11782</v>
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="D37" s="12" t="n">
-        <v>31870</v>
+        <v>35720</v>
       </c>
       <c r="E37" s="12" t="n">
         <v>13446</v>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="D38" s="12" t="n">
-        <v>33200</v>
+        <v>37200</v>
       </c>
       <c r="E38" s="12" t="n">
         <v>13446</v>
@@ -3563,7 +3563,7 @@
         </is>
       </c>
       <c r="D39" s="12" t="n">
-        <v>33200</v>
+        <v>37200</v>
       </c>
       <c r="E39" s="12" t="n">
         <v>13446</v>
@@ -3594,7 +3594,7 @@
         </is>
       </c>
       <c r="D40" s="12" t="n">
-        <v>33200</v>
+        <v>37200</v>
       </c>
       <c r="E40" s="12" t="n">
         <v>13446</v>
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="D41" s="12" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="E41" s="12" t="n">
         <v>14516</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="D42" s="12" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="E42" s="12" t="n">
         <v>14516</v>
@@ -3687,7 +3687,7 @@
         </is>
       </c>
       <c r="D43" s="12" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="E43" s="12" t="n">
         <v>14516</v>
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="D44" s="12" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="E44" s="12" t="n">
         <v>14516</v>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="D45" s="12" t="n">
-        <v>37500</v>
+        <v>42000</v>
       </c>
       <c r="E45" s="12" t="n">
         <v>15158</v>
@@ -3780,7 +3780,7 @@
         </is>
       </c>
       <c r="D46" s="12" t="n">
-        <v>37500</v>
+        <v>42000</v>
       </c>
       <c r="E46" s="12" t="n">
         <v>15158</v>
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="D47" s="12" t="n">
-        <v>37500</v>
+        <v>42000</v>
       </c>
       <c r="E47" s="12" t="n">
         <v>15158</v>
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="D48" s="12" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
       <c r="E48" s="12" t="n">
         <v>16384</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="D49" s="12" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
       <c r="E49" s="12" t="n">
         <v>16384</v>
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="D50" s="12" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
       <c r="E50" s="12" t="n">
         <v>16384</v>
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="D51" s="12" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
       <c r="E51" s="12" t="n">
         <v>16384</v>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="D52" s="12" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
       <c r="E52" s="12" t="n">
         <v>16384</v>
@@ -3997,7 +3997,7 @@
         </is>
       </c>
       <c r="D53" s="12" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
       <c r="E53" s="12" t="n">
         <v>16384</v>
@@ -4028,7 +4028,7 @@
         </is>
       </c>
       <c r="D54" s="12" t="n">
-        <v>131400</v>
+        <v>147100</v>
       </c>
       <c r="E54" s="12" t="n">
         <v>89070</v>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="D55" s="12" t="n">
-        <v>92600</v>
+        <v>103700</v>
       </c>
       <c r="E55" s="12" t="n">
         <v>59908</v>
@@ -4090,7 +4090,7 @@
         </is>
       </c>
       <c r="D56" s="12" t="n">
-        <v>89400</v>
+        <v>100100</v>
       </c>
       <c r="E56" s="12" t="n">
         <v>54678</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="D57" s="12" t="n">
-        <v>106000</v>
+        <v>118600</v>
       </c>
       <c r="E57" s="12" t="n">
         <v>74966</v>
@@ -4152,7 +4152,7 @@
         </is>
       </c>
       <c r="D58" s="12" t="n">
-        <v>86100</v>
+        <v>96400</v>
       </c>
       <c r="E58" s="12" t="n">
         <v>61664</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="D59" s="12" t="n">
-        <v>74900</v>
+        <v>83900</v>
       </c>
       <c r="E59" s="12" t="n">
         <v>52264</v>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="D60" s="12" t="n">
-        <v>80300</v>
+        <v>89900</v>
       </c>
       <c r="E60" s="12" t="n">
         <v>59534</v>
@@ -4245,7 +4245,7 @@
         </is>
       </c>
       <c r="D61" s="12" t="n">
-        <v>112700</v>
+        <v>126300</v>
       </c>
       <c r="E61" s="12" t="n">
         <v>72976</v>
@@ -4276,7 +4276,7 @@
         </is>
       </c>
       <c r="D62" s="12" t="n">
-        <v>135800</v>
+        <v>152100</v>
       </c>
       <c r="E62" s="12" t="n">
         <v>96920</v>
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="D63" s="12" t="n">
-        <v>86200</v>
+        <v>96500</v>
       </c>
       <c r="E63" s="12" t="n">
         <v>53590</v>
@@ -4338,7 +4338,7 @@
         </is>
       </c>
       <c r="D64" s="12" t="n">
-        <v>75100</v>
+        <v>84200</v>
       </c>
       <c r="E64" s="12" t="n">
         <v>55440</v>
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="D65" s="12" t="n">
-        <v>70800</v>
+        <v>79300</v>
       </c>
       <c r="E65" s="12" t="n">
         <v>52288</v>
@@ -4400,7 +4400,7 @@
         </is>
       </c>
       <c r="D66" s="12" t="n">
-        <v>113300</v>
+        <v>126900</v>
       </c>
       <c r="E66" s="12" t="n">
         <v>87174</v>
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="D67" s="12" t="n">
-        <v>69700</v>
+        <v>78100</v>
       </c>
       <c r="E67" s="12" t="n">
         <v>53408</v>
@@ -4462,7 +4462,7 @@
         </is>
       </c>
       <c r="D68" s="12" t="n">
-        <v>97500</v>
+        <v>109100</v>
       </c>
       <c r="E68" s="12" t="n">
         <v>74216</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="D69" s="12" t="n">
-        <v>129300</v>
+        <v>144800</v>
       </c>
       <c r="E69" s="12" t="n">
         <v>88896</v>
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="D70" s="12" t="n">
-        <v>129400</v>
+        <v>144900</v>
       </c>
       <c r="E70" s="12" t="n">
         <v>94290</v>
@@ -4555,7 +4555,7 @@
         </is>
       </c>
       <c r="D71" s="12" t="n">
-        <v>104400</v>
+        <v>116900</v>
       </c>
       <c r="E71" s="12" t="n">
         <v>68016</v>
@@ -4586,7 +4586,7 @@
         </is>
       </c>
       <c r="D72" s="12" t="n">
-        <v>92400</v>
+        <v>103400</v>
       </c>
       <c r="E72" s="12" t="n">
         <v>66240</v>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="D73" s="12" t="n">
-        <v>103200</v>
+        <v>115600</v>
       </c>
       <c r="E73" s="12" t="n">
         <v>73792</v>
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="D74" s="12" t="n">
-        <v>127600</v>
+        <v>143000</v>
       </c>
       <c r="E74" s="12" t="n">
         <v>91520</v>
@@ -4679,7 +4679,7 @@
         </is>
       </c>
       <c r="D75" s="12" t="n">
-        <v>109600</v>
+        <v>122800</v>
       </c>
       <c r="E75" s="12" t="n">
         <v>72720</v>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="D76" s="12" t="n">
-        <v>130700</v>
+        <v>146300</v>
       </c>
       <c r="E76" s="12" t="n">
         <v>95368</v>
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="D77" s="12" t="n">
-        <v>33000</v>
+        <v>37000</v>
       </c>
       <c r="E77" s="12" t="n">
         <v>25742</v>
@@ -4772,7 +4772,7 @@
         </is>
       </c>
       <c r="D78" s="12" t="n">
-        <v>23404</v>
+        <v>25374</v>
       </c>
       <c r="E78" s="12" t="n">
         <v>13526</v>
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="D79" s="12" t="n">
-        <v>25886</v>
+        <v>28056</v>
       </c>
       <c r="E79" s="12" t="n">
         <v>14988</v>
@@ -4834,7 +4834,7 @@
         </is>
       </c>
       <c r="D80" s="12" t="n">
-        <v>26839</v>
+        <v>29044</v>
       </c>
       <c r="E80" s="12" t="n">
         <v>15644</v>
@@ -4865,7 +4865,7 @@
         </is>
       </c>
       <c r="D81" s="12" t="n">
-        <v>27013</v>
+        <v>29290</v>
       </c>
       <c r="E81" s="12" t="n">
         <v>15600</v>
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="D82" s="12" t="n">
-        <v>21052</v>
+        <v>22765</v>
       </c>
       <c r="E82" s="12" t="n">
         <v>12306</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="D83" s="12" t="n">
-        <v>21875</v>
+        <v>23665</v>
       </c>
       <c r="E83" s="12" t="n">
         <v>12762</v>
@@ -4958,7 +4958,7 @@
         </is>
       </c>
       <c r="D84" s="12" t="n">
-        <v>21586</v>
+        <v>23449</v>
       </c>
       <c r="E84" s="12" t="n">
         <v>12384</v>
@@ -4989,7 +4989,7 @@
         </is>
       </c>
       <c r="D85" s="12" t="n">
-        <v>19543</v>
+        <v>21245</v>
       </c>
       <c r="E85" s="12" t="n">
         <v>11162</v>
@@ -5020,7 +5020,7 @@
         </is>
       </c>
       <c r="D86" s="12" t="n">
-        <v>17760</v>
+        <v>19288</v>
       </c>
       <c r="E86" s="12" t="n">
         <v>9960</v>
@@ -5051,7 +5051,7 @@
         </is>
       </c>
       <c r="D87" s="12" t="n">
-        <v>19764</v>
+        <v>21418</v>
       </c>
       <c r="E87" s="12" t="n">
         <v>11222</v>
@@ -5082,7 +5082,7 @@
         </is>
       </c>
       <c r="D88" s="12" t="n">
-        <v>19955</v>
+        <v>21677</v>
       </c>
       <c r="E88" s="12" t="n">
         <v>11168</v>
@@ -5113,7 +5113,7 @@
         </is>
       </c>
       <c r="D89" s="12" t="n">
-        <v>22298</v>
+        <v>24166</v>
       </c>
       <c r="E89" s="12" t="n">
         <v>12648</v>
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="D90" s="12" t="n">
-        <v>25686</v>
+        <v>27966</v>
       </c>
       <c r="E90" s="12" t="n">
         <v>14252</v>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="D91" s="12" t="n">
-        <v>29579</v>
+        <v>32083</v>
       </c>
       <c r="E91" s="12" t="n">
         <v>16702</v>
@@ -5206,7 +5206,7 @@
         </is>
       </c>
       <c r="D92" s="12" t="n">
-        <v>31480</v>
+        <v>34106</v>
       </c>
       <c r="E92" s="12" t="n">
         <v>17858</v>
@@ -5237,7 +5237,7 @@
         </is>
       </c>
       <c r="D93" s="12" t="n">
-        <v>29572</v>
+        <v>32108</v>
       </c>
       <c r="E93" s="12" t="n">
         <v>16608</v>
@@ -5268,7 +5268,7 @@
         </is>
       </c>
       <c r="D94" s="12" t="n">
-        <v>24600</v>
+        <v>26678</v>
       </c>
       <c r="E94" s="12" t="n">
         <v>13894</v>
@@ -5299,7 +5299,7 @@
         </is>
       </c>
       <c r="D95" s="12" t="n">
-        <v>23087</v>
+        <v>25067</v>
       </c>
       <c r="E95" s="12" t="n">
         <v>12970</v>
@@ -5330,7 +5330,7 @@
         </is>
       </c>
       <c r="D96" s="12" t="n">
-        <v>29063</v>
+        <v>31592</v>
       </c>
       <c r="E96" s="12" t="n">
         <v>16234</v>
@@ -5361,7 +5361,7 @@
         </is>
       </c>
       <c r="D97" s="12" t="n">
-        <v>29463</v>
+        <v>32082</v>
       </c>
       <c r="E97" s="12" t="n">
         <v>16324</v>
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="D98" s="12" t="n">
-        <v>25145</v>
+        <v>27260</v>
       </c>
       <c r="E98" s="12" t="n">
         <v>14220</v>
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="D99" s="12" t="n">
-        <v>28907</v>
+        <v>31373</v>
       </c>
       <c r="E99" s="12" t="n">
         <v>16266</v>
@@ -5454,7 +5454,7 @@
         </is>
       </c>
       <c r="D100" s="12" t="n">
-        <v>31137</v>
+        <v>33810</v>
       </c>
       <c r="E100" s="12" t="n">
         <v>17478</v>
@@ -5485,7 +5485,7 @@
         </is>
       </c>
       <c r="D101" s="12" t="n">
-        <v>3375</v>
+        <v>3681</v>
       </c>
       <c r="E101" s="12" t="n">
         <v>1856</v>
@@ -5505,7 +5505,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -5557,7 +5557,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -5601,17 +5601,17 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>162000</v>
+        <v>181400</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>135400</v>
+        <v>151700</v>
       </c>
       <c r="D6" s="13">
         <f>IF(C6=0,"",B6/C6-1)</f>
         <v/>
       </c>
       <c r="E6" s="12" t="n">
-        <v>96464</v>
+        <v>115864</v>
       </c>
       <c r="F6" s="13">
         <f>IF(B6=0,"",E6/B6)</f>
@@ -5625,17 +5625,17 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>400900</v>
+        <v>449100</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>367900</v>
+        <v>412100</v>
       </c>
       <c r="D7" s="13">
         <f>IF(C7=0,"",B7/C7-1)</f>
         <v/>
       </c>
       <c r="E7" s="12" t="n">
-        <v>115550</v>
+        <v>163750</v>
       </c>
       <c r="F7" s="13">
         <f>IF(B7=0,"",E7/B7)</f>
@@ -5649,17 +5649,17 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>88564</v>
+        <v>96124</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>79777</v>
+        <v>86549</v>
       </c>
       <c r="D8" s="13">
         <f>IF(C8=0,"",B8/C8-1)</f>
         <v/>
       </c>
       <c r="E8" s="12" t="n">
-        <v>38744</v>
+        <v>46304</v>
       </c>
       <c r="F8" s="13">
         <f>IF(B8=0,"",E8/B8)</f>
@@ -5673,17 +5673,17 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>651464</v>
+        <v>726624</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>583077</v>
+        <v>650349</v>
       </c>
       <c r="D9" s="13">
         <f>IF(C9=0,"",B9/C9-1)</f>
         <v/>
       </c>
       <c r="E9" s="12" t="n">
-        <v>250758</v>
+        <v>325918</v>
       </c>
       <c r="F9" s="13">
         <f>IF(B9=0,"",E9/B9)</f>
@@ -5696,7 +5696,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-10/growth-trades.xlsx
+++ b/media/exports/reports/2026-10/growth-trades.xlsx
@@ -818,7 +818,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B17" s="9">
-        <f>Workings!B38</f>
+        <f>Workings!B36</f>
         <v/>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B29" s="9">
-        <f>Workings!B69</f>
+        <f>Workings!B67</f>
         <v/>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="B41" s="9">
-        <f>Workings!B100</f>
+        <f>Workings!B98</f>
         <v/>
       </c>
       <c r="C41" s="10" t="inlineStr">
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="B53" s="9">
-        <f>Workings!B131</f>
+        <f>Workings!B129</f>
         <v/>
       </c>
       <c r="C53" s="10" t="inlineStr">
@@ -1315,7 +1315,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1360,7 +1360,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2481,7 +2481,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -5505,7 +5505,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -5557,7 +5557,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
